--- a/VerveStacks_IND_grids_kan/SuppXLS/Scen_TSParameters_ts_12t.xlsx
+++ b/VerveStacks_IND_grids_kan/SuppXLS/Scen_TSParameters_ts_12t.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C7D10AD-66FA-488C-A71A-F33CCEAE1BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A35C449-1894-45C1-97A6-4BAFAACF31BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1287,10 +1287,10 @@
     <t>day_night</t>
   </si>
   <si>
-    <t>FaD,SaD,RaD,FaP,SaP,WaD,WaP,RaP</t>
+    <t>RaD,FaD,FaP,SaP,WaD,WaP,RaP,SaD</t>
   </si>
   <si>
-    <t>RaP,FaP,SaP,SaN,WaN,WaP,FaN,RaN</t>
+    <t>SaN,WaN,WaP,RaP,RaN,FaP,SaP,FaN</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>RaP,FaP,SaP,SaN,WaN,WaP,FaN,RaN</v>
+        <v>SaN,WaN,WaP,RaP,RaN,FaP,SaP,FaN</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>FaD,SaD,RaD,FaP,SaP,WaD,WaP,RaP</v>
+        <v>RaD,FaD,FaP,SaP,WaD,WaP,RaP,SaD</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -2013,7 +2013,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E395B2EB-D841-434A-B189-2D5ED4FB07FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98ADB256-D317-4813-A0DE-56327D206CA1}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2097,7 +2097,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3158185F-83F6-4744-9E67-163442068933}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CF613AA-D79E-463D-813F-BC25D7196974}">
   <dimension ref="B9:O946"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -28367,7 +28367,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEFD8C4F-9FF1-4136-AF7C-F8FCF2C2809C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AA607AF-E6D6-4774-B5B1-0675123D2AD6}">
   <dimension ref="B9:BL179"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -44885,7 +44885,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32D2FE5B-3E17-414E-9F3D-66C08F5E2506}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D4F8FC-D054-4745-9EC9-7CFC3AE785CF}">
   <dimension ref="B9:E22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -45083,7 +45083,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7915D3F9-E114-4F5E-BFA0-4F4FC8BD4BA8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8765CB30-917D-4E06-9035-74531584A11E}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -45374,7 +45374,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD29D33E-3C1F-42E8-A218-4B1905C9F775}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51C85F4F-9352-425F-90EB-0C374DCD9188}">
   <dimension ref="B9:D22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -45533,7 +45533,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{971B8D99-DAB3-4BFC-B496-2B85119001D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{740EBD71-2B55-4F0E-9015-428A2E40B30A}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -45565,7 +45565,7 @@
         <v>37</v>
       </c>
       <c r="D11">
-        <v>0.43716666666666665</v>
+        <v>0.4371666666666667</v>
       </c>
       <c r="E11" t="s">
         <v>422</v>
@@ -45607,7 +45607,7 @@
         <v>45</v>
       </c>
       <c r="D14">
-        <v>0.26990000000000003</v>
+        <v>0.26989999999999997</v>
       </c>
       <c r="E14" t="s">
         <v>422</v>
@@ -45649,7 +45649,7 @@
         <v>43</v>
       </c>
       <c r="D17">
-        <v>0.56513333333333327</v>
+        <v>0.56513333333333338</v>
       </c>
       <c r="E17" t="s">
         <v>422</v>
@@ -45705,7 +45705,7 @@
         <v>43</v>
       </c>
       <c r="D21">
-        <v>0.57656666666666678</v>
+        <v>0.57656666666666667</v>
       </c>
       <c r="E21" t="s">
         <v>422</v>
@@ -45733,7 +45733,7 @@
         <v>37</v>
       </c>
       <c r="D23">
-        <v>0.48210000000000003</v>
+        <v>0.48209999999999997</v>
       </c>
       <c r="E23" t="s">
         <v>422</v>
@@ -45761,7 +45761,7 @@
         <v>43</v>
       </c>
       <c r="D25">
-        <v>0.58203333333333329</v>
+        <v>0.5820333333333334</v>
       </c>
       <c r="E25" t="s">
         <v>422</v>
@@ -45789,7 +45789,7 @@
         <v>37</v>
       </c>
       <c r="D27">
-        <v>0.4201333333333333</v>
+        <v>0.42013333333333341</v>
       </c>
       <c r="E27" t="s">
         <v>422</v>
@@ -45831,7 +45831,7 @@
         <v>45</v>
       </c>
       <c r="D30">
-        <v>0.21880000000000002</v>
+        <v>0.21879999999999999</v>
       </c>
       <c r="E30" t="s">
         <v>422</v>
@@ -45873,7 +45873,7 @@
         <v>43</v>
       </c>
       <c r="D33">
-        <v>0.49940000000000001</v>
+        <v>0.4993999999999999</v>
       </c>
       <c r="E33" t="s">
         <v>422</v>
@@ -46013,7 +46013,7 @@
         <v>37</v>
       </c>
       <c r="D43">
-        <v>0.37929999999999997</v>
+        <v>0.37930000000000003</v>
       </c>
       <c r="E43" t="s">
         <v>422</v>
@@ -46111,7 +46111,7 @@
         <v>45</v>
       </c>
       <c r="D50">
-        <v>0.18899999999999997</v>
+        <v>0.18900000000000003</v>
       </c>
       <c r="E50" t="s">
         <v>422</v>
@@ -46209,7 +46209,7 @@
         <v>43</v>
       </c>
       <c r="D57">
-        <v>0.43830000000000008</v>
+        <v>0.43829999999999997</v>
       </c>
       <c r="E57" t="s">
         <v>422</v>
@@ -46237,7 +46237,7 @@
         <v>37</v>
       </c>
       <c r="D59">
-        <v>0.40466666666666673</v>
+        <v>0.40466666666666667</v>
       </c>
       <c r="E59" t="s">
         <v>422</v>
@@ -46279,7 +46279,7 @@
         <v>45</v>
       </c>
       <c r="D62">
-        <v>0.23069999999999999</v>
+        <v>0.23070000000000002</v>
       </c>
       <c r="E62" t="s">
         <v>422</v>
@@ -46321,7 +46321,7 @@
         <v>43</v>
       </c>
       <c r="D65">
-        <v>0.47416666666666668</v>
+        <v>0.47416666666666663</v>
       </c>
       <c r="E65" t="s">
         <v>422</v>
@@ -46335,7 +46335,7 @@
         <v>45</v>
       </c>
       <c r="D66">
-        <v>0.24303333333333335</v>
+        <v>0.24303333333333332</v>
       </c>
       <c r="E66" t="s">
         <v>422</v>
@@ -46391,7 +46391,7 @@
         <v>45</v>
       </c>
       <c r="D70">
-        <v>0.23089999999999999</v>
+        <v>0.23090000000000002</v>
       </c>
       <c r="E70" t="s">
         <v>422</v>
@@ -46489,7 +46489,7 @@
         <v>43</v>
       </c>
       <c r="D77">
-        <v>0.48763333333333336</v>
+        <v>0.48763333333333331</v>
       </c>
       <c r="E77" t="s">
         <v>422</v>
@@ -46615,7 +46615,7 @@
         <v>45</v>
       </c>
       <c r="D86">
-        <v>0.26106666666666667</v>
+        <v>0.26106666666666661</v>
       </c>
       <c r="E86" t="s">
         <v>422</v>
@@ -46671,7 +46671,7 @@
         <v>45</v>
       </c>
       <c r="D90">
-        <v>0.2869666666666667</v>
+        <v>0.28696666666666665</v>
       </c>
       <c r="E90" t="s">
         <v>422</v>
@@ -46727,7 +46727,7 @@
         <v>45</v>
       </c>
       <c r="D94">
-        <v>0.28143333333333337</v>
+        <v>0.28143333333333331</v>
       </c>
       <c r="E94" t="s">
         <v>422</v>
@@ -46741,7 +46741,7 @@
         <v>37</v>
       </c>
       <c r="D95">
-        <v>0.49489999999999995</v>
+        <v>0.49490000000000006</v>
       </c>
       <c r="E95" t="s">
         <v>422</v>
@@ -46783,7 +46783,7 @@
         <v>45</v>
       </c>
       <c r="D98">
-        <v>0.24973333333333333</v>
+        <v>0.24973333333333336</v>
       </c>
       <c r="E98" t="s">
         <v>422</v>
@@ -46825,7 +46825,7 @@
         <v>43</v>
       </c>
       <c r="D101">
-        <v>0.50543333333333329</v>
+        <v>0.5054333333333334</v>
       </c>
       <c r="E101" t="s">
         <v>422</v>
@@ -47063,7 +47063,7 @@
         <v>45</v>
       </c>
       <c r="D118">
-        <v>0.22640000000000002</v>
+        <v>0.22639999999999996</v>
       </c>
       <c r="E118" t="s">
         <v>422</v>
@@ -47105,7 +47105,7 @@
         <v>43</v>
       </c>
       <c r="D121">
-        <v>0.49280000000000007</v>
+        <v>0.49279999999999996</v>
       </c>
       <c r="E121" t="s">
         <v>422</v>
